--- a/NuevasNotas/Vespertina/Resultados_Auditoria_Notas/Matriz_Marcada_7AV.xlsx
+++ b/NuevasNotas/Vespertina/Resultados_Auditoria_Notas/Matriz_Marcada_7AV.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,10 +58,16 @@
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -91,24 +97,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="003B82F6"/>
+        <bgColor rgb="003B82F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E5E7EB"/>
         <bgColor rgb="00E5E7EB"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F3F4F6"/>
-        <bgColor rgb="00F3F4F6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -174,11 +174,16 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -223,20 +228,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,6 +434,12 @@
       <text>
         <t>Sistema: 9.08
 Diferencia: 0.04</t>
+      </text>
+    </comment>
+    <comment ref="J30" authorId="0" shapeId="0">
+      <text>
+        <t>Sistema: 8.56
+Diferencia: 0.50</t>
       </text>
     </comment>
     <comment ref="J31" authorId="0" shapeId="0">
@@ -798,13 +813,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -816,846 +832,652 @@
       <c r="B1" s="16" t="n"/>
       <c r="C1" s="16" t="n"/>
       <c r="D1" s="16" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Curso</t>
-        </is>
-      </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="E1" s="16" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>▶ CURSO: 7AV</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Estudiante</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Tipo de Problema</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
-        <is>
-          <t>Detalle de la Discrepancia</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>Materia</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>Docente</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>ARIAS GUIRACOCHA CHRISTOPHER ADONIS</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
-        <is>
-          <t>Educación Física (Docente: 8.37 vs Sistema: 8.73)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>Educación Física</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>8.73</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>BARRERA MENDOZA JHON MARIO</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t>Lengua y Literatura (Docente: 8.17 vs Sistema: 8.05)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>BRITO ASTUDILLO RAUL MATBO</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>BRITO ASTUDILLO RAUL MATEO</t>
-        </is>
-      </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>7AV</t>
+          <t>Lengua y Literatura</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>8.050000000000001</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>CHACA GUACHICHULLCA AMY SOFIA</t>
         </is>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>CHACA GUACHICHULLCA AMY SOFIA</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>Inglés (Docente: 8.58 vs Sistema: 8.55)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>7AV</t>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>8.550000000000001</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>CRUZ TORRES DANIEL FERNANDO</t>
         </is>
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>CRUZ TORRES DANIEL FERNANDO</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>CRUZ TORRES DANIEL FERNANDO</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>Matemática (Docente: 8.39 vs Sistema: 8.11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>CRUZ TORRES DANIEL FERNANDO</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>8.109999999999999</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="E9" s="21" t="n">
+        <v>8.02</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>Estudios Sociales</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>8.640000000000001</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>Educación Cultural y Artística</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>8.69</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>Educación Física</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>8.48</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="23" t="n"/>
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>8.369999999999999</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>CUERO MAZA RANDY MANUEL</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>Ciencias Naturales (Docente: 8.23 vs Sistema: 8.02)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>CRUZ TORRES DANIEL FERNANDO</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>8.68</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>Estudios Sociales</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>8.720000000000001</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="E17" s="21" t="n">
+        <v>7.24</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Educación Cultural y Artística</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="E18" s="21" t="n">
+        <v>8.92</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>Educación Física</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="E19" s="21" t="n">
+        <v>8.359999999999999</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="23" t="n"/>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>DELGADO SALTOS ANDREA GEOVANNA</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>Estudios Sociales (Docente: 8.87 vs Sistema: 8.64)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>CRUZ TORRES DANIEL FERNANDO</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>Estudios Sociales</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="E21" s="19" t="n">
+        <v>9.890000000000001</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>LOOR CRUZ RUTH ANAHI</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>Educación Cultural y Artística (Docente: 8.85 vs Sistema: 8.69)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="25" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>CRUZ TORRES DANIEL FERNANDO</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>9.08</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>MALLA OCHOA ERICK ANIBAL</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>Educación Física (Docente: 8.36 vs Sistema: 8.48)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>CRUZ TORRES DANIEL FERNANDO</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>Educación Física</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="E23" s="19" t="n">
+        <v>8.56</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>MAZA FERNANDEZ NAYELI ESTEFANIA</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.33 vs Sistema: 8.37)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>CUERO MAZA RANDY MANUEL</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>⚠️ DESFASE</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>Inconsistencia en la nómina del estudiante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="25" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>CUERO MAZA RANDY MANUEL</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>Educación Física</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="E24" s="19" t="n">
+        <v>8.869999999999999</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>MOROCHO MALLA GABRIELA JHOMARA</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>Matemática (Docente: 8.4 vs Sistema: 8.68)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="25" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>CUERO MAZA RANDY MANUEL</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="E25" s="21" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="23" t="n"/>
+      <c r="B26" s="23" t="n"/>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>Educación Física</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>9.42</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>PINEDA CAMPOVERDE IRIS GUADALUPE</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>Ciencias Naturales (Docente: 8.1 vs Sistema: 8.3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="25" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>CUERO MAZA RANDY MANUEL</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="E27" s="21" t="n">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="23" t="n"/>
+      <c r="B28" s="23" t="n"/>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>Educación Física</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="E28" s="19" t="n">
+        <v>9.130000000000001</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>PINTA VASQUEZ MAYLI XIOMARA</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>Estudios Sociales (Docente: 8.5 vs Sistema: 8.72)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="25" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>CUERO MAZA RANDY MANUEL</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>Educación Física</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="E29" s="19" t="n">
+        <v>9.380000000000001</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>PUIN GUALLPA ADRIANA NICOLE</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>Inglés (Docente: 7.28 vs Sistema: 7.24)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="25" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
-        <is>
-          <t>CUERO MAZA RANDY MANUEL</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>Educación Física</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="E30" s="19" t="n">
+        <v>8.69</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>PULGARIN SACA AZUCENA MILENA</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>Educación Cultural y Artística (Docente: 8.78 vs Sistema: 8.92)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="25" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>CUERO MAZA RANDY MANUEL</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>Educación Física</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="E31" s="19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>QUITO CAGUANA JULIAN ALEXANDER</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>Educación Física (Docente: 8.48 vs Sistema: 8.36)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="25" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>CUERO MAZA RANDY MANUEL</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>Inglés</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="E32" s="21" t="n">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>Educación Física</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E33" s="21" t="n">
+        <v>9.09</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="23" t="n"/>
+      <c r="B34" s="23" t="n"/>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>Promedio Final / P. General</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E34" s="19" t="n">
+        <v>8.789999999999999</v>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>QUIZHPI SANCHEZ EVELYN BELINDA</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.37 vs Sistema: 8.33)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="25" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>DELGADO SALTOS ANDREA GEOVANNA</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>Educación Física</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="E35" s="19" t="n">
+        <v>9.529999999999999</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>SAMANIEGO CABRERA LEONEL MATIAS</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>❌ ERROR DE NOTA</t>
         </is>
       </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>Estudios Sociales (Docente: 9.71 vs Sistema: 9.89)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="25" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>LOOR CRUZ RUTH ANAHI</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>Inglés (Docente: 9.04 vs Sistema: 9.08)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="25" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>MALLA OCHOA ERICK ANIBAL</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN SISTEMA</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>El estudiante está en la matriz del docente pero no en el reporte oficial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="25" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B26" s="21" t="inlineStr">
-        <is>
-          <t>MALLA OCHOA ERICK ANIVAL</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>⚠️ FALTA EN DOCENTE</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="inlineStr">
-        <is>
-          <t>El estudiante está en el reporte oficial pero falta en la matriz del docente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="25" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>MAZA FERNANDEZ NAYELI ESTEFANIA</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>Educación Física (Docente: 8.56 vs Sistema: 8.87)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="25" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>MOROCHO MALLA GABRIELA JHOMARA</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>Inglés (Docente: 8.43 vs Sistema: 8.4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="25" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>MOROCHO MALLA GABRIELA JHOMARA</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>Educación Física (Docente: 8.87 vs Sistema: 9.42)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="25" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B30" s="21" t="inlineStr">
-        <is>
-          <t>PINEDA CAMPOVERDE IRIS GUADALUPE</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr">
-        <is>
-          <t>Inglés (Docente: 9.78 vs Sistema: 9.75)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="25" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>PINEDA CAMPOVERDE IRIS GUADALUPE</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>Educación Física (Docente: 9.42 vs Sistema: 9.13)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="25" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B32" s="21" t="inlineStr">
-        <is>
-          <t>PINTA VASQUEZ MAYLI XIOMARA</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D32" s="21" t="inlineStr">
-        <is>
-          <t>Educación Física (Docente: 9.13 vs Sistema: 9.38)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="25" customHeight="1">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>PUIN GUALLPA ADRIANA NICOLE</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>Educación Física (Docente: 9.38 vs Sistema: 8.69)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="25" customHeight="1">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B34" s="21" t="inlineStr">
-        <is>
-          <t>PULGARIN SACA AZUCENA MILENA</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="inlineStr">
-        <is>
-          <t>Educación Física (Docente: 8.69 vs Sistema: 8.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="25" customHeight="1">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>QUITO CAGUANA JULIAN ALEXANDER</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>Inglés (Docente: 8.28 vs Sistema: 8.25)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="25" customHeight="1">
-      <c r="A36" s="20" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B36" s="21" t="inlineStr">
-        <is>
-          <t>QUITO CAGUANA JULIAN ALEXANDER</t>
-        </is>
-      </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D36" s="21" t="inlineStr">
-        <is>
-          <t>Educación Física (Docente: 8.2 vs Sistema: 9.09)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="25" customHeight="1">
-      <c r="A37" s="18" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B37" s="19" t="inlineStr">
-        <is>
-          <t>QUITO CAGUANA JULIAN ALEXANDER</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D37" s="19" t="inlineStr">
-        <is>
-          <t>Promedio Final / P. General (Docente: 8.7 vs Sistema: 8.79)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="25" customHeight="1">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B38" s="21" t="inlineStr">
-        <is>
-          <t>QUIZHPI SANCHEZ EVELYN BELINDA</t>
-        </is>
-      </c>
-      <c r="C38" s="20" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="inlineStr">
-        <is>
-          <t>Educación Física (Docente: 9.09 vs Sistema: 9.53)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="25" customHeight="1">
-      <c r="A39" s="18" t="inlineStr">
-        <is>
-          <t>7AV</t>
-        </is>
-      </c>
-      <c r="B39" s="19" t="inlineStr">
-        <is>
-          <t>SAMANIEGO CABRERA LEONEL MATIAS</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="inlineStr">
-        <is>
-          <t>❌ ERROR DE NOTA</t>
-        </is>
-      </c>
-      <c r="D39" s="19" t="inlineStr">
-        <is>
-          <t>Educación Física (Docente: 9.53 vs Sistema: 8.26)</t>
-        </is>
+          <t>Educación Física</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="E36" s="19" t="n">
+        <v>8.26</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="12">
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B8:B13"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A14:A20"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="B14:B20"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3206,7 +3028,7 @@
           <t>115100483-3</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>MALLA OCHOA ERICK ANIBAL</t>
         </is>
@@ -3229,7 +3051,7 @@
       <c r="I30" s="9" t="n">
         <v>8.56</v>
       </c>
-      <c r="J30" s="9" t="n">
+      <c r="J30" s="15" t="n">
         <v>9.06</v>
       </c>
       <c r="K30" s="7" t="inlineStr">
